--- a/terminology/ValueSet-registering-provider-service-type-cz.xlsx
+++ b/terminology/ValueSet-registering-provider-service-type-cz.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,19 +114,10 @@
     <t>310061009</t>
   </si>
   <si>
-    <t>gynekologické služby</t>
-  </si>
-  <si>
     <t>700232004</t>
   </si>
   <si>
-    <t>všeobecné lékařské služby</t>
-  </si>
-  <si>
     <t>722176000</t>
-  </si>
-  <si>
-    <t>stomatologické služby</t>
   </si>
   <si>
     <t/>
@@ -428,40 +419,34 @@
       <c r="A2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>33</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
